--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/jul-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/jul-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>37416.03</v>
+        <v>37771.44</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>58737.79</v>
+        <v>59295.73</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>17598.1</v>
+        <v>17666.79</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>37402.92</v>
+        <v>37548.93</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>761.21</v>
+        <v>764.1799999999999</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>30664.9</v>
+        <v>30973.31</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>22445.72</v>
+        <v>22670.48</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>18411.12</v>
+        <v>18595.48</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>35276.11</v>
+        <v>35455.87</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1192.86</v>
+        <v>1198.94</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>43518.97</v>
+        <v>43688.38</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>52378.42</v>
+        <v>52582.32</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>36977.88</v>
+        <v>37056.7</v>
       </c>
     </row>
     <row r="15">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>72361.03999999999</v>
+        <v>72526.98</v>
       </c>
     </row>
     <row r="16">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>32858.35</v>
+        <v>33078.29</v>
       </c>
     </row>
     <row r="17">
@@ -1488,7 +1488,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>28862.8</v>
+        <v>29055.99</v>
       </c>
     </row>
     <row r="18">
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>30611.34</v>
+        <v>30816.24</v>
       </c>
     </row>
     <row r="19">
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>107346.32</v>
+        <v>108064.84</v>
       </c>
     </row>
     <row r="20">
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>120712.8</v>
+        <v>121520.79</v>
       </c>
     </row>
     <row r="21">
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>22095.45</v>
+        <v>22025.65</v>
       </c>
     </row>
     <row r="22">
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>48560.21</v>
+        <v>48454.56</v>
       </c>
     </row>
     <row r="23">
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>15940.47</v>
+        <v>15908.52</v>
       </c>
     </row>
     <row r="24">
@@ -1923,7 +1923,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>17244.69</v>
+        <v>17210.12</v>
       </c>
     </row>
     <row r="25">
@@ -1984,7 +1984,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>398.55</v>
+        <v>397.75</v>
       </c>
     </row>
     <row r="26">
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>75591.86</v>
+        <v>75440.33</v>
       </c>
     </row>
     <row r="27">
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>73244.25</v>
+        <v>72820.3</v>
       </c>
     </row>
     <row r="28">
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>712.6799999999999</v>
+        <v>708.55</v>
       </c>
     </row>
     <row r="29">
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>41999.21</v>
+        <v>41321.44</v>
       </c>
     </row>
     <row r="30">
@@ -2289,7 +2289,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>721.13</v>
+        <v>709.49</v>
       </c>
     </row>
     <row r="31">
@@ -2350,7 +2350,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>35561.57</v>
+        <v>34987.69</v>
       </c>
     </row>
     <row r="32">
@@ -2411,7 +2411,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1362.08</v>
+        <v>1340.1</v>
       </c>
     </row>
     <row r="33">
@@ -2472,7 +2472,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>693.99</v>
+        <v>682.79</v>
       </c>
     </row>
     <row r="34">
@@ -2533,7 +2533,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>169017.9</v>
+        <v>166290.37</v>
       </c>
     </row>
     <row r="35">
@@ -2594,7 +2594,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1119.35</v>
+        <v>1101.28</v>
       </c>
     </row>
     <row r="36">
@@ -2655,7 +2655,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>41386.51</v>
+        <v>40718.63</v>
       </c>
     </row>
     <row r="37">
@@ -2716,7 +2716,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>597.45</v>
+        <v>587.8099999999999</v>
       </c>
     </row>
     <row r="38">
@@ -2777,7 +2777,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>29858.07</v>
+        <v>29376.24</v>
       </c>
     </row>
     <row r="39">
@@ -2838,7 +2838,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>32923.19</v>
+        <v>32391.89</v>
       </c>
     </row>
     <row r="40">
@@ -2899,7 +2899,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>22719.1</v>
+        <v>22354.83</v>
       </c>
     </row>
     <row r="41">
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>32224.45</v>
+        <v>31707.78</v>
       </c>
     </row>
     <row r="42">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>26853.71</v>
+        <v>26541.25</v>
       </c>
     </row>
     <row r="43">
@@ -3082,7 +3082,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>31943.13</v>
+        <v>31571.45</v>
       </c>
     </row>
     <row r="44">
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>38267.34</v>
+        <v>37822.07</v>
       </c>
     </row>
     <row r="45">
@@ -3204,7 +3204,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>37580.16</v>
+        <v>37371.82</v>
       </c>
     </row>
     <row r="46">
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>32200.06</v>
+        <v>32021.55</v>
       </c>
     </row>
     <row r="47">
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>32541.86</v>
+        <v>32361.45</v>
       </c>
     </row>
     <row r="48">
@@ -3387,7 +3387,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>34599.4</v>
+        <v>34429.28</v>
       </c>
     </row>
     <row r="49">
@@ -3448,7 +3448,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>34372.75</v>
+        <v>34203.75</v>
       </c>
     </row>
     <row r="50">
@@ -3509,7 +3509,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>32092.94</v>
+        <v>31935.15</v>
       </c>
     </row>
     <row r="51">
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>33732.67</v>
+        <v>33566.81</v>
       </c>
     </row>
     <row r="52">
@@ -3631,7 +3631,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>36686.67</v>
+        <v>36932.23</v>
       </c>
     </row>
     <row r="53">
@@ -3692,7 +3692,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>46897.23</v>
+        <v>47211.13</v>
       </c>
     </row>
     <row r="54">
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>650188.38</v>
+        <v>654540.41</v>
       </c>
     </row>
     <row r="55">
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>17186.38</v>
+        <v>17301.41</v>
       </c>
     </row>
     <row r="56">
@@ -3879,7 +3879,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1473.5</v>
+        <v>1483.36</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/jul-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/jul-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC jul-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC jul-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/jul-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/jul-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M56"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -554,7 +554,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
+          <t>Ilustre Municipalidad de Curepto</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1372,7 +1372,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>926853-51-CM26</t>
+          <t>4034-309-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1392,48 +1392,52 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>65.120.506-9</t>
+          <t>69.160.501-9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Valdivia</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>DIFOR CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>96.918.300-5</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>33078.29</v>
+        <v>108064.84</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>650-72-CM26</t>
+          <t>646-74-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1453,32 +1457,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.814.000-8</t>
+          <t>61.816.000-9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION II REGION</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION IV REGION</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
+          <t>76.349.970-7</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1488,13 +1492,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>29055.99</v>
+        <v>30816.24</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>646-74-CM26</t>
+          <t>5240-180-SE26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1514,48 +1518,52 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.816.000-9</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION IV REGION</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.349.970-7</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>30816.24</v>
+        <v>121520.79</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4034-309-CM26</t>
+          <t>650-72-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1575,52 +1583,48 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.160.501-9</t>
+          <t>61.814.000-8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cañete - Educación</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION II REGION</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>DIFOR CHILE SOCIEDAD ANONIMA</t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>96.918.300-5</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>O'Higgins</t>
-        </is>
-      </c>
+          <t>84.807.200-1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>108064.84</v>
+        <v>29055.99</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5240-180-SE26</t>
+          <t>926853-51-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1645,41 +1649,37 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>65.120.506-9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>121520.79</v>
+        <v>33078.29</v>
       </c>
     </row>
     <row r="21">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1746,7 +1746,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3801-36-CM26</t>
+          <t>377-311-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1771,27 +1771,27 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.172.600-2</t>
+          <t>69.061.600-9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILACO</t>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>AUTO SUMMIT CHILE S.A.</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>96.924.460-8</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1801,13 +1801,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>48454.56</v>
+        <v>731.05</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2483-461-CM26</t>
+          <t>3801-36-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1822,37 +1822,37 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.071.300-4</t>
+          <t>69.172.600-2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILICURA</t>
+          <t>I MUNICIPALIDAD DE QUILACO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>AUTO SUMMIT CHILE S.A.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>96.924.460-8</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>15908.52</v>
+        <v>48454.56</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3820-637-CM26</t>
+          <t>2483-461-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1888,32 +1888,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.051.000-6</t>
+          <t>69.071.300-4</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
+          <t>I MUNICIPALIDAD DE QUILICURA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1923,13 +1923,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>17210.12</v>
+        <v>15908.52</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3820-638-CM26</t>
+          <t>3820-637-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1984,13 +1984,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>397.75</v>
+        <v>17210.12</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>564953-704-CM26</t>
+          <t>3820-638-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2010,32 +2010,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>70.902.000-5</t>
+          <t>69.051.000-6</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>CORP DE EDUCACION Y SALUD DE LAS CONDES</t>
+          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2045,13 +2045,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>75440.33</v>
+        <v>397.75</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1195-408-CM26</t>
+          <t>564953-704-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2076,17 +2076,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>70.902.000-5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>72820.3</v>
+        <v>75440.33</v>
       </c>
     </row>
     <row r="28">
@@ -2173,7 +2173,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1596-185-CM26</t>
+          <t>1195-408-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2228,13 +2228,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>41321.44</v>
+        <v>72820.3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2688-237-CM26</t>
+          <t>5240-169-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2254,32 +2254,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.061.600-9</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>86.385.500-4</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2289,13 +2289,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>709.49</v>
+        <v>166290.37</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2688-236-CM26</t>
+          <t>1743-372-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2320,27 +2320,27 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.061.600-9</t>
+          <t>69.091.100-0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+          <t>I MUNICIPALIDAD DE LITUECHE</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2350,13 +2350,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>34987.69</v>
+        <v>29376.24</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1596-186-CM26</t>
+          <t>1743-373-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2381,27 +2381,27 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>69.091.100-0</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>I MUNICIPALIDAD DE LITUECHE</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2411,13 +2411,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1340.1</v>
+        <v>587.8099999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1077195-70-CM26</t>
+          <t>1743-374-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2442,17 +2442,17 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>82.983.100-7</t>
+          <t>69.091.100-0</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Administración de Fondos de Terceros</t>
+          <t>I MUNICIPALIDAD DE LITUECHE</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2472,13 +2472,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>682.79</v>
+        <v>40718.63</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5240-169-CM26</t>
+          <t>1743-375-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2503,27 +2503,27 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>69.091.100-0</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE LITUECHE</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
+          <t>76.027.979-k</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>166290.37</v>
+        <v>1101.28</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1743-375-CM26</t>
+          <t>1077195-69-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2564,17 +2564,17 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.091.100-0</t>
+          <t>82.983.100-7</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LITUECHE</t>
+          <t>Comisión Chilena de Energía Nuclear</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2594,13 +2594,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1101.28</v>
+        <v>32391.89</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1743-374-CM26</t>
+          <t>1077195-70-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2625,17 +2625,17 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.091.100-0</t>
+          <t>82.983.100-7</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LITUECHE</t>
+          <t>Comisión Chilena de Energía Nuclear</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2655,13 +2655,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>40718.63</v>
+        <v>682.79</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1743-373-CM26</t>
+          <t>1596-185-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2686,27 +2686,27 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.091.100-0</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LITUECHE</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2716,13 +2716,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>587.8099999999999</v>
+        <v>41321.44</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1743-372-CM26</t>
+          <t>1596-186-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2747,27 +2747,27 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.091.100-0</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LITUECHE</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2777,13 +2777,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>29376.24</v>
+        <v>1340.1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1077195-69-CM26</t>
+          <t>2688-236-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2808,17 +2808,17 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>82.983.100-7</t>
+          <t>69.061.600-9</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Administración de Fondos de Terceros</t>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2838,13 +2838,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>32391.89</v>
+        <v>34987.69</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1590-206-CM26</t>
+          <t>2688-237-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2869,27 +2869,27 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.301.000-9</t>
+          <t>69.061.600-9</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE AGRICULT</t>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>76.027.979-k</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2899,13 +2899,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>22354.83</v>
+        <v>709.49</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1422035-16-CM26</t>
+          <t>1590-206-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>65.034.681-5</t>
+          <t>61.301.000-9</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DEL MAULE</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE AGRICULT</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2945,12 +2945,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2960,13 +2960,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>31707.78</v>
+        <v>22354.83</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1195104-212-CM26</t>
+          <t>1422035-16-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2981,37 +2981,37 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>62.000.920-2</t>
+          <t>65.034.681-5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE MIGRACIONES</t>
+          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DEL MAULE</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>H. Motores S.A.</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.124.915-0</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3021,13 +3021,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>26541.25</v>
+        <v>31707.78</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2885-339-CM26</t>
+          <t>4236-511-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3052,27 +3052,27 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>69.210.600-8</t>
+          <t>69.160.200-1</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUYEHUE</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3082,13 +3082,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>31571.45</v>
+        <v>37822.07</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4236-511-CM26</t>
+          <t>1195104-212-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3108,32 +3108,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.160.200-1</t>
+          <t>62.000.920-2</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
+          <t>SERVICIO NACIONAL DE MIGRACIONES</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>H. Motores S.A.</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>76.124.915-0</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3143,13 +3143,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>37822.07</v>
+        <v>26541.25</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4083-352-CM26</t>
+          <t>2885-339-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3174,27 +3174,27 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.151.002-6</t>
+          <t>69.210.600-8</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO DEPARTAMENTO DE SALUD</t>
+          <t>I MUNICIPALIDAD DE PUYEHUE</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3204,7 +3204,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>37371.82</v>
+        <v>31571.45</v>
       </c>
     </row>
     <row r="46">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3332,7 +3332,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1180885-32-CM26</t>
+          <t>4083-352-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3357,27 +3357,27 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>69.151.002-6</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3387,13 +3387,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>34429.28</v>
+        <v>37371.82</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>4494-544-CM26</t>
+          <t>2780-248-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3413,32 +3413,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.150.500-6</t>
+          <t>69.050.100-7</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCO</t>
+          <t>I MUNICIPALIDAD DE LA LIGUA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3448,13 +3448,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>34203.75</v>
+        <v>33566.81</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2291-1276-CM26</t>
+          <t>1180885-32-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3479,27 +3479,27 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>76.027.979-k</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>31935.15</v>
+        <v>34429.28</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2780-248-CM26</t>
+          <t>4494-544-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3540,27 +3540,27 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.050.100-7</t>
+          <t>69.150.500-6</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA LIGUA</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3570,13 +3570,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>33566.81</v>
+        <v>34203.75</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2429-914-CM26</t>
+          <t>2291-1276-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3601,27 +3601,27 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3631,13 +3631,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>36932.23</v>
+        <v>31935.15</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1216088-218-CM26</t>
+          <t>2963-81-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3662,12 +3662,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>65.065.121-9</t>
+          <t>69.072.400-6</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES DE PUENTE ALTO</t>
+          <t>I MUNICIPALIDAD DE LA GRANJA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3677,12 +3677,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3692,13 +3692,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>47211.13</v>
+        <v>17301.41</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1782-12-CM26</t>
+          <t>2429-914-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>72.224.100-2</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Gobierno Regional de Antofagasta</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3738,32 +3738,28 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>654540.41</v>
+        <v>36932.23</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2963-81-CM26</t>
+          <t>1216088-218-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3788,12 +3784,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>69.072.400-6</t>
+          <t>65.065.121-9</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA GRANJA</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES DE PUENTE ALTO</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3803,12 +3799,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3818,67 +3814,132 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>17301.41</v>
+        <v>47211.13</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>1782-12-CM26</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>72.224.100-2</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>BRUNO FRITSCH S.A.</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>84.807.200-1</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>654540.41</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>2429-915-CM26</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2239-6-LR25</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>jul-2026</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
         <is>
           <t>69.020.300-6</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>Antofagasta</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="n">
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="n">
         <v>1483.36</v>
       </c>
     </row>

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/jul-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/jul-2026.xlsx
@@ -562,7 +562,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +883,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +948,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1013,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1078,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1143,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1208,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1334,11 @@
           <t>96.918.300-5</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1611,7 +1655,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1672,7 +1720,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1733,7 +1785,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1794,7 +1850,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1916,7 +1976,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1977,7 +2041,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2038,7 +2106,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2099,7 +2171,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2160,7 +2236,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2221,7 +2301,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2343,7 +2427,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2404,7 +2492,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2709,7 +2801,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2770,7 +2866,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2953,7 +3053,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3014,7 +3118,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3075,7 +3183,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3136,7 +3248,11 @@
           <t>76.124.915-0</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3197,7 +3313,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3258,7 +3378,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3319,7 +3443,11 @@
           <t>76.124.915-0</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3380,7 +3508,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3441,7 +3573,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3563,7 +3699,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3624,7 +3764,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3685,7 +3829,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3746,7 +3894,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3807,7 +3959,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3933,7 +4089,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/jul-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/jul-2026.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
